--- a/weeks/◆ 2026년 10월 2주 편성표 (1005 ~ 1011).xlsx
+++ b/weeks/◆ 2026년 10월 2주 편성표 (1005 ~ 1011).xlsx
@@ -485,11 +485,11 @@
     <xf numFmtId="49" fontId="34" fillId="8" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="10" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="49" fontId="35" fillId="7" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+      <alignment wrapText="true" horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="10" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="7" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="37" fillId="6" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
@@ -508,48 +508,48 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="6.0"/>
-    <col min="2" max="2" customWidth="true" width="0.375"/>
-    <col min="3" max="3" customWidth="true" width="5.125"/>
-    <col min="4" max="4" customWidth="true" width="3.625"/>
-    <col min="5" max="5" customWidth="true" width="2.125"/>
-    <col min="6" max="6" customWidth="true" width="3.625"/>
-    <col min="7" max="7" customWidth="true" width="16.375"/>
-    <col min="8" max="8" customWidth="true" width="0.375"/>
-    <col min="9" max="9" customWidth="true" width="5.125"/>
-    <col min="10" max="10" customWidth="true" width="3.625"/>
-    <col min="11" max="11" customWidth="true" width="2.125"/>
-    <col min="12" max="12" customWidth="true" width="3.625"/>
-    <col min="13" max="13" customWidth="true" width="16.375"/>
-    <col min="14" max="14" customWidth="true" width="0.375"/>
-    <col min="15" max="15" customWidth="true" width="5.125"/>
-    <col min="16" max="16" customWidth="true" width="3.625"/>
-    <col min="17" max="17" customWidth="true" width="2.125"/>
-    <col min="18" max="18" customWidth="true" width="3.625"/>
-    <col min="19" max="19" customWidth="true" width="16.375"/>
-    <col min="20" max="20" customWidth="true" width="0.375"/>
-    <col min="21" max="21" customWidth="true" width="5.125"/>
-    <col min="22" max="22" customWidth="true" width="3.625"/>
-    <col min="23" max="23" customWidth="true" width="2.125"/>
-    <col min="24" max="24" customWidth="true" width="3.625"/>
-    <col min="25" max="25" customWidth="true" width="16.375"/>
-    <col min="26" max="26" customWidth="true" width="0.375"/>
-    <col min="27" max="27" customWidth="true" width="5.125"/>
-    <col min="28" max="28" customWidth="true" width="3.625"/>
-    <col min="29" max="29" customWidth="true" width="2.125"/>
-    <col min="30" max="30" customWidth="true" width="3.625"/>
-    <col min="31" max="31" customWidth="true" width="16.375"/>
-    <col min="32" max="32" customWidth="true" width="0.375"/>
-    <col min="33" max="33" customWidth="true" width="5.125"/>
-    <col min="34" max="34" customWidth="true" width="3.625"/>
-    <col min="35" max="35" customWidth="true" width="2.125"/>
-    <col min="36" max="36" customWidth="true" width="3.625"/>
-    <col min="37" max="37" customWidth="true" width="16.375"/>
-    <col min="38" max="38" customWidth="true" width="0.375"/>
-    <col min="39" max="39" customWidth="true" width="5.125"/>
-    <col min="40" max="40" customWidth="true" width="3.625"/>
-    <col min="41" max="41" customWidth="true" width="2.125"/>
-    <col min="42" max="42" customWidth="true" width="3.625"/>
-    <col min="43" max="43" customWidth="true" width="16.625"/>
+    <col min="2" max="2" customWidth="true" width="0.25"/>
+    <col min="3" max="3" customWidth="true" width="3.75"/>
+    <col min="4" max="4" customWidth="true" width="2.625"/>
+    <col min="5" max="5" customWidth="true" width="1.5"/>
+    <col min="6" max="6" customWidth="true" width="2.625"/>
+    <col min="7" max="7" customWidth="true" width="11.875"/>
+    <col min="8" max="8" customWidth="true" width="0.25"/>
+    <col min="9" max="9" customWidth="true" width="3.75"/>
+    <col min="10" max="10" customWidth="true" width="2.625"/>
+    <col min="11" max="11" customWidth="true" width="1.5"/>
+    <col min="12" max="12" customWidth="true" width="2.625"/>
+    <col min="13" max="13" customWidth="true" width="11.875"/>
+    <col min="14" max="14" customWidth="true" width="0.25"/>
+    <col min="15" max="15" customWidth="true" width="3.75"/>
+    <col min="16" max="16" customWidth="true" width="2.625"/>
+    <col min="17" max="17" customWidth="true" width="1.5"/>
+    <col min="18" max="18" customWidth="true" width="2.625"/>
+    <col min="19" max="19" customWidth="true" width="11.875"/>
+    <col min="20" max="20" customWidth="true" width="0.25"/>
+    <col min="21" max="21" customWidth="true" width="3.75"/>
+    <col min="22" max="22" customWidth="true" width="2.625"/>
+    <col min="23" max="23" customWidth="true" width="1.5"/>
+    <col min="24" max="24" customWidth="true" width="2.625"/>
+    <col min="25" max="25" customWidth="true" width="11.875"/>
+    <col min="26" max="26" customWidth="true" width="0.25"/>
+    <col min="27" max="27" customWidth="true" width="3.75"/>
+    <col min="28" max="28" customWidth="true" width="2.625"/>
+    <col min="29" max="29" customWidth="true" width="1.5"/>
+    <col min="30" max="30" customWidth="true" width="2.625"/>
+    <col min="31" max="31" customWidth="true" width="11.875"/>
+    <col min="32" max="32" customWidth="true" width="0.25"/>
+    <col min="33" max="33" customWidth="true" width="3.75"/>
+    <col min="34" max="34" customWidth="true" width="2.625"/>
+    <col min="35" max="35" customWidth="true" width="1.5"/>
+    <col min="36" max="36" customWidth="true" width="2.625"/>
+    <col min="37" max="37" customWidth="true" width="11.875"/>
+    <col min="38" max="38" customWidth="true" width="0.25"/>
+    <col min="39" max="39" customWidth="true" width="3.75"/>
+    <col min="40" max="40" customWidth="true" width="2.625"/>
+    <col min="41" max="41" customWidth="true" width="1.5"/>
+    <col min="42" max="42" customWidth="true" width="2.625"/>
+    <col min="43" max="43" customWidth="true" width="11.625"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="true" ht="24.75">
@@ -596,7 +596,7 @@
       <c r="AK1" s="4"/>
       <c r="AL1" s="4" t="inlineStr">
         <is>
-          <t>1차 확정안입니다.</t>
+          <t>확정 편성표입니다.</t>
         </is>
       </c>
       <c r="AM1" s="4"/>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AK9" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">보넬드 당근주스 </t>
+          <t>(재) 이경제 흑염소진액</t>
         </is>
       </c>
       <c r="AL9" s="25"/>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="S10" s="30" t="inlineStr">
         <is>
-          <t>셀폰즈 녹는실 앰플</t>
+          <t>브이티 아이크림</t>
         </is>
       </c>
       <c r="T10" s="25"/>
@@ -1900,12 +1900,12 @@
       </c>
       <c r="R13" s="30" t="inlineStr">
         <is>
-          <t>'패션1Lab'</t>
+          <t>'패션2Lab'</t>
         </is>
       </c>
       <c r="S13" s="33" t="inlineStr">
         <is>
-          <t>누캐시미어 라쿤울 베스트</t>
+          <t xml:space="preserve">라이317 FAUX레더자켓 </t>
         </is>
       </c>
       <c r="T13" s="25"/>
@@ -2141,18 +2141,18 @@
       </c>
       <c r="AC14" s="31" t="inlineStr">
         <is>
-          <t>수
+          <t>중
 수</t>
         </is>
       </c>
       <c r="AD14" s="30" t="inlineStr">
         <is>
-          <t>'뷰티브랜드'</t>
+          <t>'뷰티2'</t>
         </is>
       </c>
       <c r="AE14" s="30" t="inlineStr">
         <is>
-          <t>프라우카 세이지 크림</t>
+          <t>셀폰즈 녹는실 앰플</t>
         </is>
       </c>
       <c r="AF14" s="25"/>
@@ -2254,17 +2254,17 @@
       </c>
       <c r="K15" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>중</t>
         </is>
       </c>
       <c r="L15" s="30" t="inlineStr">
         <is>
-          <t>'뷰티2'</t>
+          <t>'주방'</t>
         </is>
       </c>
       <c r="M15" s="30" t="inlineStr">
         <is>
-          <t>실크테라피 에센스</t>
+          <t>더스텐 유리용기</t>
         </is>
       </c>
       <c r="N15" s="25"/>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="W15" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>중</t>
         </is>
       </c>
       <c r="X15" s="30" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="AD15" s="30" t="inlineStr">
         <is>
-          <t>'잡화'</t>
+          <t>'건강식품1'</t>
         </is>
       </c>
       <c r="AE15" s="30" t="inlineStr">
         <is>
-          <t>스케쳐스 맥스런 운동화</t>
+          <t>덴마크유산균(금 가능)</t>
         </is>
       </c>
       <c r="AF15" s="25"/>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="Z16" s="25"/>
-      <c r="AA16" s="37" t="inlineStr">
+      <c r="AA16" s="29" t="inlineStr">
         <is>
           <t>13:35</t>
         </is>
@@ -2524,17 +2524,17 @@
       </c>
       <c r="AC16" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>수</t>
         </is>
       </c>
       <c r="AD16" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AE16" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'잡화'</t>
+        </is>
+      </c>
+      <c r="AE16" s="30" t="inlineStr">
+        <is>
+          <t>스케쳐스 맥스런 운동화</t>
         </is>
       </c>
       <c r="AF16" s="25"/>
@@ -2610,17 +2610,17 @@
       </c>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>중</t>
         </is>
       </c>
       <c r="F17" s="30" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="G17" s="36" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
+          <t>언더웨어</t>
+        </is>
+      </c>
+      <c r="G17" s="30" t="inlineStr">
+        <is>
+          <t>라코스테드로즈</t>
         </is>
       </c>
       <c r="H17" s="25"/>
@@ -2642,12 +2642,12 @@
       </c>
       <c r="L17" s="30" t="inlineStr">
         <is>
-          <t>'가전'</t>
+          <t>'일반렌탈'</t>
         </is>
       </c>
       <c r="M17" s="30" t="inlineStr">
         <is>
-          <t>삼성 냉장고</t>
+          <t>청호나이스 정수기 렌탈</t>
         </is>
       </c>
       <c r="N17" s="25"/>
@@ -2677,29 +2677,30 @@
         </is>
       </c>
       <c r="T17" s="25"/>
-      <c r="U17" s="37" t="inlineStr">
+      <c r="U17" s="29" t="inlineStr">
         <is>
           <t>13:15</t>
         </is>
       </c>
-      <c r="V17" s="24" t="inlineStr">
+      <c r="V17" s="34" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="W17" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="W17" s="31" t="inlineStr">
+        <is>
+          <t>대
+수</t>
         </is>
       </c>
       <c r="X17" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="Y17" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'가전'</t>
+        </is>
+      </c>
+      <c r="Y17" s="40" t="inlineStr">
+        <is>
+          <t>LG 공기청정기</t>
         </is>
       </c>
       <c r="Z17" s="25"/>
@@ -2756,7 +2757,7 @@
         </is>
       </c>
       <c r="AL17" s="25"/>
-      <c r="AM17" s="37" t="inlineStr">
+      <c r="AM17" s="29" t="inlineStr">
         <is>
           <t>16:10</t>
         </is>
@@ -2766,19 +2767,20 @@
           <t>65</t>
         </is>
       </c>
-      <c r="AO17" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="AO17" s="31" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="AP17" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AQ17" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'리빙'</t>
+        </is>
+      </c>
+      <c r="AQ17" s="30" t="inlineStr">
+        <is>
+          <t>플로너스디퓨저</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2813,7 @@
       </c>
       <c r="G18" s="30" t="inlineStr">
         <is>
-          <t>디아루체 글리터 뷔스티에 3종</t>
+          <t>에바큐브 캐시미어 베스트</t>
         </is>
       </c>
       <c r="H18" s="25"/>
@@ -2831,7 +2833,7 @@
 수</t>
         </is>
       </c>
-      <c r="L18" s="40" t="inlineStr">
+      <c r="L18" s="41" t="inlineStr">
         <is>
           <t>'리빙'</t>
         </is>
@@ -2854,17 +2856,17 @@
       </c>
       <c r="Q18" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>대</t>
         </is>
       </c>
       <c r="R18" s="30" t="inlineStr">
         <is>
-          <t>'액티브라이프'</t>
+          <t>'뷰티2'</t>
         </is>
       </c>
       <c r="S18" s="30" t="inlineStr">
         <is>
-          <t>신덕재 두부면</t>
+          <t>실크테라피 에센스</t>
         </is>
       </c>
       <c r="T18" s="25"/>
@@ -2873,7 +2875,7 @@
           <t>14:05</t>
         </is>
       </c>
-      <c r="V18" s="24" t="inlineStr">
+      <c r="V18" s="34" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -2886,12 +2888,12 @@
       </c>
       <c r="X18" s="30" t="inlineStr">
         <is>
-          <t>'건강식품2'</t>
-        </is>
-      </c>
-      <c r="Y18" s="30" t="inlineStr">
-        <is>
-          <t>종근당건강 맥스19</t>
+          <t>'가전'</t>
+        </is>
+      </c>
+      <c r="Y18" s="40" t="inlineStr">
+        <is>
+          <t>LG 건조기</t>
         </is>
       </c>
       <c r="Z18" s="25"/>
@@ -2907,7 +2909,7 @@
       </c>
       <c r="AC18" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>중</t>
         </is>
       </c>
       <c r="AD18" s="30" t="inlineStr">
@@ -3017,23 +3019,24 @@
           <t>50</t>
         </is>
       </c>
-      <c r="K19" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
+      <c r="K19" s="31" t="inlineStr">
+        <is>
+          <t>대
+수</t>
         </is>
       </c>
       <c r="L19" s="30" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="M19" s="39" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
+          <t>'가전'</t>
+        </is>
+      </c>
+      <c r="M19" s="30" t="inlineStr">
+        <is>
+          <t>삼성 냉장고</t>
         </is>
       </c>
       <c r="N19" s="25"/>
-      <c r="O19" s="37" t="inlineStr">
+      <c r="O19" s="29" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
@@ -3050,12 +3053,12 @@
       </c>
       <c r="R19" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="S19" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'액티브라이프'</t>
+        </is>
+      </c>
+      <c r="S19" s="30" t="inlineStr">
+        <is>
+          <t>신덕재 두부면</t>
         </is>
       </c>
       <c r="T19" s="25"/>
@@ -3064,25 +3067,24 @@
           <t>14:55</t>
         </is>
       </c>
-      <c r="V19" s="34" t="inlineStr">
+      <c r="V19" s="24" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="W19" s="31" t="inlineStr">
-        <is>
-          <t>대
-수</t>
+      <c r="W19" s="24" t="inlineStr">
+        <is>
+          <t>대</t>
         </is>
       </c>
       <c r="X19" s="30" t="inlineStr">
         <is>
-          <t>'가전'</t>
-        </is>
-      </c>
-      <c r="Y19" s="41" t="inlineStr">
-        <is>
-          <t>LG 공기청정기</t>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="Y19" s="39" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
         </is>
       </c>
       <c r="Z19" s="25"/>
@@ -3091,7 +3093,7 @@
           <t>16:30</t>
         </is>
       </c>
-      <c r="AB19" s="34" t="inlineStr">
+      <c r="AB19" s="24" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -3106,7 +3108,7 @@
           <t>'패션2Lab'</t>
         </is>
       </c>
-      <c r="AE19" s="41" t="inlineStr">
+      <c r="AE19" s="30" t="inlineStr">
         <is>
           <t>이상봉 넥카프 3종</t>
         </is>
@@ -3138,7 +3140,7 @@
         </is>
       </c>
       <c r="AL19" s="25"/>
-      <c r="AM19" s="37" t="inlineStr">
+      <c r="AM19" s="29" t="inlineStr">
         <is>
           <t>18:25</t>
         </is>
@@ -3155,12 +3157,12 @@
       </c>
       <c r="AP19" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AQ19" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'리빙'</t>
+        </is>
+      </c>
+      <c r="AQ19" s="30" t="inlineStr">
+        <is>
+          <t>보이러 전기요</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3256,7 @@
           <t>15:45</t>
         </is>
       </c>
-      <c r="V20" s="34" t="inlineStr">
+      <c r="V20" s="24" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -3267,21 +3269,21 @@
       </c>
       <c r="X20" s="30" t="inlineStr">
         <is>
-          <t>'가전'</t>
-        </is>
-      </c>
-      <c r="Y20" s="41" t="inlineStr">
-        <is>
-          <t>LG 건조기</t>
+          <t>'건강식품2'</t>
+        </is>
+      </c>
+      <c r="Y20" s="30" t="inlineStr">
+        <is>
+          <t>종근당건강 맥스19</t>
         </is>
       </c>
       <c r="Z20" s="25"/>
-      <c r="AA20" s="29" t="inlineStr">
+      <c r="AA20" s="37" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="AB20" s="34" t="inlineStr">
+      <c r="AB20" s="24" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -3293,12 +3295,12 @@
       </c>
       <c r="AD20" s="30" t="inlineStr">
         <is>
-          <t>'패션3Lab'</t>
-        </is>
-      </c>
-      <c r="AE20" s="41" t="inlineStr">
-        <is>
-          <t>머티리얼랩 레이스 니트 집업 外</t>
+          <t>Hit &amp; Best</t>
+        </is>
+      </c>
+      <c r="AE20" s="38" t="inlineStr">
+        <is>
+          <t>Hit &amp; Best</t>
         </is>
       </c>
       <c r="AF20" s="25"/>
@@ -3411,7 +3413,7 @@
       </c>
       <c r="M21" s="42" t="inlineStr">
         <is>
-          <t>(첫)박준면 파김치</t>
+          <t>해남 호박고구마</t>
         </is>
       </c>
       <c r="N21" s="25"/>
@@ -3437,7 +3439,7 @@
       </c>
       <c r="S21" s="33" t="inlineStr">
         <is>
-          <t>해남 호박고구마</t>
+          <t>(첫)박준면 파김치</t>
         </is>
       </c>
       <c r="T21" s="25"/>
@@ -3472,7 +3474,7 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="AB21" s="24" t="inlineStr">
+      <c r="AB21" s="34" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -3484,12 +3486,12 @@
       </c>
       <c r="AD21" s="30" t="inlineStr">
         <is>
-          <t>'잡화'</t>
-        </is>
-      </c>
-      <c r="AE21" s="30" t="inlineStr">
-        <is>
-          <t>슈올즈 포브</t>
+          <t>'패션3Lab'</t>
+        </is>
+      </c>
+      <c r="AE21" s="40" t="inlineStr">
+        <is>
+          <t>머티리얼랩 레이스 니트 집업 外</t>
         </is>
       </c>
       <c r="AF21" s="25"/>
@@ -3576,7 +3578,7 @@
       </c>
       <c r="G22" s="42" t="inlineStr">
         <is>
-          <t>프로쉬 주방세제</t>
+          <t>팀P-프로쉬 주방세제</t>
         </is>
       </c>
       <c r="H22" s="25"/>
@@ -3665,7 +3667,7 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="AB22" s="24" t="inlineStr">
+      <c r="AB22" s="34" t="inlineStr">
         <is>
           <t>75</t>
         </is>
@@ -3681,7 +3683,7 @@
           <t>'패션2Lab'</t>
         </is>
       </c>
-      <c r="AE22" s="30" t="inlineStr">
+      <c r="AE22" s="40" t="inlineStr">
         <is>
           <t>리오벨 26 pre-winter 풀스킨 렉스퍼 야상 자켓</t>
         </is>
@@ -3770,7 +3772,7 @@
       </c>
       <c r="G23" s="42" t="inlineStr">
         <is>
-          <t>알레보 유리 밥용기</t>
+          <t>팀P-알레보 유리 밥용기</t>
         </is>
       </c>
       <c r="H23" s="25"/>
@@ -3796,7 +3798,7 @@
       </c>
       <c r="M23" s="42" t="inlineStr">
         <is>
-          <t>브리타 정수기</t>
+          <t>사업부P-브리타 정수기</t>
         </is>
       </c>
       <c r="N23" s="25"/>
@@ -3906,7 +3908,7 @@
         </is>
       </c>
       <c r="AL23" s="25"/>
-      <c r="AM23" s="37" t="inlineStr">
+      <c r="AM23" s="29" t="inlineStr">
         <is>
           <t>22:45</t>
         </is>
@@ -3918,17 +3920,17 @@
       </c>
       <c r="AO23" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>대</t>
         </is>
       </c>
       <c r="AP23" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AQ23" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="AQ23" s="39" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
         </is>
       </c>
     </row>
@@ -3951,17 +3953,17 @@
       </c>
       <c r="E24" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>수</t>
         </is>
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="G24" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'가전'</t>
+        </is>
+      </c>
+      <c r="G24" s="42" t="inlineStr">
+        <is>
+          <t>황쇼 다이슨에어랩</t>
         </is>
       </c>
       <c r="H24" s="25"/>
@@ -4519,7 +4521,7 @@
         </is>
       </c>
       <c r="H27" s="25"/>
-      <c r="I27" s="29" t="inlineStr">
+      <c r="I27" s="37" t="inlineStr">
         <is>
           <t>22:55</t>
         </is>
@@ -4529,20 +4531,19 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K27" s="31" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="L27" s="30" t="inlineStr">
         <is>
-          <t>'잡화'</t>
-        </is>
-      </c>
-      <c r="M27" s="30" t="inlineStr">
-        <is>
-          <t>베라왕 로퍼</t>
+          <t>Hit &amp; Best</t>
+        </is>
+      </c>
+      <c r="M27" s="38" t="inlineStr">
+        <is>
+          <t>Hit &amp; Best</t>
         </is>
       </c>
       <c r="N27" s="25"/>
@@ -4707,21 +4708,21 @@
       </c>
       <c r="K28" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>대</t>
         </is>
       </c>
       <c r="L28" s="30" t="inlineStr">
         <is>
-          <t>'리빙'</t>
-        </is>
-      </c>
-      <c r="M28" s="30" t="inlineStr">
-        <is>
-          <t>보이러 전기요</t>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="M28" s="39" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
         </is>
       </c>
       <c r="N28" s="25"/>
-      <c r="O28" s="29" t="inlineStr">
+      <c r="O28" s="37" t="inlineStr">
         <is>
           <t>23:55</t>
         </is>
@@ -4733,17 +4734,17 @@
       </c>
       <c r="Q28" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>중</t>
         </is>
       </c>
       <c r="R28" s="30" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="S28" s="39" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
+          <t>Hit &amp; Best</t>
+        </is>
+      </c>
+      <c r="S28" s="38" t="inlineStr">
+        <is>
+          <t>Hit &amp; Best</t>
         </is>
       </c>
       <c r="T28" s="25"/>
